--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R2834103be4c24ed7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R87488879a5b64c81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R13f1e24c20f34318"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rf3f279797cd14d13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R164080655c4e42ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R4e39c8b2cd0b43e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R4a455858d5624968"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R39ec330de4564487"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Ra36a079337774a1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R0e7d8b302a8c4b1a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -424,7 +424,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d067a428cac4241"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc01c1cf5c11e4a8d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1002,7 +1002,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6272ce0ea456443e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R777fe7313cb54401"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1130,7 +1130,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0eb5ffa718e24ad6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c37173117144fc5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1490,7 +1490,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40c80e8c9e284b4a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f651286b3994098"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1578,7 +1578,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0e706c549604e8d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R951a0bb611fc4e2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R4e39c8b2cd0b43e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R4a455858d5624968"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R39ec330de4564487"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Ra36a079337774a1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R0e7d8b302a8c4b1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Red5ac6439d254372"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Raa526f72741140e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R384c29c45b064056"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Reef3a81169f34796"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Re0e032c5740a407a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -424,7 +424,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc01c1cf5c11e4a8d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0bc6d42d33cc425f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1002,7 +1002,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R777fe7313cb54401"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b1c655105084785"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1042,7 +1042,7 @@
         <x:v>output/release_readiness.json|output/reports/auth_flow_matrix.csv|output/reports/focus_recovery.csv|output/reports/locale_copy_findings.csv|output/tests/login-webauthn-fallback.spec.ts</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>与交付压缩包根目录逐字一致</x:v>
+        <x:v>与任务指定的交付路径一致</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="86" customHeight="1">
@@ -1050,13 +1050,13 @@
         <x:v>输入数据包</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>开工材料集合</x:v>
+        <x:v>业务材料集合</x:v>
       </x:c>
       <x:c r="C3" s="7" t="str">
         <x:v>input_data/README.md|input_data/app/locales/en-US.json|input_data/app/locales/es-ES.json|input_data/app/locales/zh-CN.json|input_data/app/login.html|input_data/app/login.js|input_data/package.json|input_data/playwright.config.cjs|input_data/scenarios/auth_scenarios.json|input_data/starter/login-webauthn-fallback.spec.ts|input_data/tools/run-task.mjs</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>README与入口点名业务材料</x:v>
+        <x:v>README与入口列出的登录页业务材料</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="86" customHeight="1">
@@ -1130,7 +1130,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c37173117144fc5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbae8a3d0ac24241"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1490,7 +1490,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f651286b3994098"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ac79575b2fc465b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1527,10 +1527,10 @@
         <x:v>test分组、辅助函数和报表函数可重组</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>仍从公开输入读取场景与语言，实际启动BrowserContext与page</x:v>
+        <x:v>仍从本次输入读取场景与语言，并实际启动BrowserContext与page</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>不影响固定路径、场景结果和下游用途</x:v>
+        <x:v>不影响交付路径、场景结果和下游用途</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="86" customHeight="1">
@@ -1578,7 +1578,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R951a0bb611fc4e2b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41ab99edc76745dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>